--- a/suivi_taches.xlsx
+++ b/suivi_taches.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1F06A3-8DD5-40DB-86A2-DE521F596086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D26EAE-6FA1-4F23-9276-72128FCB1E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="289">
   <si>
     <t>Catégorie</t>
   </si>
@@ -116,9 +116,6 @@
     <t>***</t>
   </si>
   <si>
-    <t>Matériel mis à disposition des clients</t>
-  </si>
-  <si>
     <t>En cours</t>
   </si>
   <si>
@@ -167,18 +164,9 @@
     <t>Murs (peintures)</t>
   </si>
   <si>
-    <t>peintre externe</t>
-  </si>
-  <si>
     <t>Nettoyage</t>
   </si>
   <si>
-    <t>Nettoyage des terrasses - nettoyage quotidien</t>
-  </si>
-  <si>
-    <t>Nettoyage des terrasses - nettoyage annuel</t>
-  </si>
-  <si>
     <t>Aménagements divers</t>
   </si>
   <si>
@@ -200,9 +188,6 @@
     <t>Extincteurs</t>
   </si>
   <si>
-    <t>Réaménagement des réserves</t>
-  </si>
-  <si>
     <t>Wellness</t>
   </si>
   <si>
@@ -221,9 +206,6 @@
     <t>Plantation parterres parking</t>
   </si>
   <si>
-    <t>Pelouse côté citadelle</t>
-  </si>
-  <si>
     <t>Borne recharge électrique supplémentaires</t>
   </si>
   <si>
@@ -437,9 +419,6 @@
     <t>en attente</t>
   </si>
   <si>
-    <t>Jean-Louis</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
@@ -449,15 +428,9 @@
     <t>Laurent</t>
   </si>
   <si>
-    <t>BEGELEC</t>
-  </si>
-  <si>
     <t>Karim</t>
   </si>
   <si>
-    <t>REXEL - ULTRASONS</t>
-  </si>
-  <si>
     <t>Paolo</t>
   </si>
   <si>
@@ -491,24 +464,12 @@
     <t>Frank</t>
   </si>
   <si>
-    <t>offre à modifier</t>
-  </si>
-  <si>
-    <t>service achats Liège</t>
-  </si>
-  <si>
-    <t>commencé par Gaby</t>
-  </si>
-  <si>
     <t>chambre Douglas</t>
   </si>
   <si>
     <t>Réglage test avant d'aller plus loin</t>
   </si>
   <si>
-    <t>FLORATOIT</t>
-  </si>
-  <si>
     <t>en cours</t>
   </si>
   <si>
@@ -557,15 +518,6 @@
     <t>Greg</t>
   </si>
   <si>
-    <t>Réparation provisoire réalisée car produit reçu n'était pas le bon</t>
-  </si>
-  <si>
-    <t>Déjà demandé plusieurs fois à VIP WELLNESS</t>
-  </si>
-  <si>
-    <t>VIP WELLNESS ne finalise pas</t>
-  </si>
-  <si>
     <t xml:space="preserve">test avec nouvelles grilles à réaliser avant modification </t>
   </si>
   <si>
@@ -608,25 +560,13 @@
     <t>chaque année</t>
   </si>
   <si>
-    <t>procédure pour contrôle du matériel</t>
-  </si>
-  <si>
     <t xml:space="preserve">NU-SWIFT info@importex.be </t>
   </si>
   <si>
     <t>commande ok - prévu +/- 1ère quinzaine de juillet</t>
   </si>
   <si>
-    <t>Alim + décharge ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reste étagères a accrocher au mur et déplacement prises data - Adrien doit faire vider armoire local coffre pour déplacer armoires métalliques </t>
-  </si>
-  <si>
     <t>reste remplacement goulotte blanche côté casino - Intervention prévue le 9/06 reportée au 11/06 puis reportée à la semaine prochaine date ???</t>
-  </si>
-  <si>
-    <t>reste radiateur - Adrien commande un IPTV - câble data à tirer</t>
   </si>
   <si>
     <t>Devis potence demandé chez ULTRASONS - rappel le 10/06</t>
@@ -654,12 +594,6 @@
     <t>Ventilation canalisations casino pour odeurs</t>
   </si>
   <si>
-    <t>AEJ rénovations Varella</t>
-  </si>
-  <si>
-    <t>Etilux</t>
-  </si>
-  <si>
     <t>Engie, RenoEnergie, Interparking ?</t>
   </si>
   <si>
@@ -684,25 +618,12 @@
     <t>stock géré par la maintenance, remplacées au fur et à mesure</t>
   </si>
   <si>
-    <t>sous contrat pour remplacement des piles</t>
-  </si>
-  <si>
-    <t>Dyler</t>
-  </si>
-  <si>
     <t>en suspens</t>
   </si>
   <si>
     <t>lors des travaux de rénovation</t>
   </si>
   <si>
-    <t>Wallon</t>
-  </si>
-  <si>
-    <t>équipement de nouveau reparti pour analyse chez le fournisseur
-réparé mais à nouveau grillé</t>
-  </si>
-  <si>
     <t>²</t>
   </si>
   <si>
@@ -712,9 +633,6 @@
     <t>Resort</t>
   </si>
   <si>
-    <t>emo liquids</t>
-  </si>
-  <si>
     <t>aménagement sortie de secours côté Meuse</t>
   </si>
   <si>
@@ -724,68 +642,9 @@
     <t>Caméras reçues 27/05 - socles peints 28/05 - installation au retour de congé de Frank</t>
   </si>
   <si>
-    <t>Nettoyage + démolitions +/- 15/08 - début travaux septembre</t>
-  </si>
-  <si>
-    <t>Devis demandé chez ULTRASONS - rappel le 10/06
-prestataire à relancer - prototype semaine 33</t>
-  </si>
-  <si>
-    <t>Visite pour second devis semaine 33</t>
-  </si>
-  <si>
-    <t>1 des 2 à été remplacé, l'autre à un problème de communication - fournisseur cherche une solution - rappel fait le 04/08</t>
-  </si>
-  <si>
-    <t>LINERGY</t>
-  </si>
-  <si>
-    <t>commandé chez SKIDATA mais responsable ne travaille plus là… - rappel le 29/07</t>
-  </si>
-  <si>
-    <t>SKIDATA</t>
-  </si>
-  <si>
-    <t>Demandes de prix faites attente offres</t>
-  </si>
-  <si>
-    <t>Rappel BEGELEC le 18/05 - attente des plans de BALTEAU - vient le 14/08</t>
-  </si>
-  <si>
-    <t>nouveau test du 10/08 au 17/08</t>
-  </si>
-  <si>
-    <t>Offre à recevoir rappel fait le 29/05
-demande envoyée à un autre prestataire - Assa Abloy ne fait plus ces portes - Demande faite chez un 3ème</t>
-  </si>
-  <si>
-    <t>RAL envoyé - prévu mi-aout</t>
-  </si>
-  <si>
-    <t>test à faire - ICT doit configurer téléphones</t>
-  </si>
-  <si>
-    <t>prestataire passé, ça vient d'en bas - test avec ventilation prévu - dosage augmenté partout dans casino</t>
-  </si>
-  <si>
-    <t>Arrêté car hôtel full - reprend le 15/06 - reste 17 chambres le 07/08</t>
-  </si>
-  <si>
-    <t>Sterfput à créer et carrelage à acheter - date carrotage à recevoir du sous-traitant</t>
-  </si>
-  <si>
-    <t>optimiser odeurs casino - dosage augmenté</t>
-  </si>
-  <si>
-    <t>2 demandes de prix demandées</t>
-  </si>
-  <si>
     <t>Fin betting</t>
   </si>
   <si>
-    <t>Bornes enlevées le 18/08 - JM et Greg doivent dire ce qu'ils veulent mettre dans la zone</t>
-  </si>
-  <si>
     <t>procédure électricité</t>
   </si>
   <si>
@@ -795,28 +654,11 @@
     <t>Betting</t>
   </si>
   <si>
-    <t>offre de prix reçue
-décision à prendre - voir Karim, Jérôme</t>
-  </si>
-  <si>
     <t>offre de Stéphane DUBOIS envoyée à JM - attente JM</t>
-  </si>
-  <si>
-    <t>Marchandise arrivée au dépôt</t>
-  </si>
-  <si>
-    <t>Visite le 11/05 - devis en attente - dernier rappel le 22/05 - rappel par email + téléphone 05/06 - réception trespa pour réparation semaine 33 - porte prix à faire diminuer</t>
-  </si>
-  <si>
-    <t>Offre à corriger et compléter - relevé à faire par Jean-Louis</t>
   </si>
   <si>
     <t>évacuation régulière en fonction de l'encombrement
 + faire appel à un container pour palettes</t>
-  </si>
-  <si>
-    <t>conteneur le 12/08
-à voir si quelqu'un peut venir les chercher</t>
   </si>
   <si>
     <t>normalement résolu par SCREEN SERVICES
@@ -825,10 +667,6 @@
 1 en réserve</t>
   </si>
   <si>
-    <t>RENO ENERGIE prépare le dossier pour les pompiers - En attente du contrat pour la partie ENGIE mais déjà lancé
-2 commandes - rapide chez Engie, normale au sous-sol chez RENO - contrat à valider par le légal</t>
-  </si>
-  <si>
     <t>Fin sol cuisine traiteur - Casino Club</t>
   </si>
   <si>
@@ -838,9 +676,6 @@
     <t>LCDR</t>
   </si>
   <si>
-    <t>Jérôme Farino - contact société</t>
-  </si>
-  <si>
     <t>recherche d'un autre prestataire</t>
   </si>
   <si>
@@ -853,14 +688,236 @@
     <t>Yacht Club</t>
   </si>
   <si>
-    <t>à mettre dans les capex
-four, électricité, hotte…</t>
-  </si>
-  <si>
-    <t>prise triphasée entrée hôtel</t>
-  </si>
-  <si>
     <t>Hôtel</t>
+  </si>
+  <si>
+    <t>Plans reçu de BALTEAU envoyé chez BEGELEC et rappel fait le 14/08</t>
+  </si>
+  <si>
+    <t>conteneur le 12/08
+à voir si quelqu'un peut venir les chercher - fait un conteneur 15 m3 évacué</t>
+  </si>
+  <si>
+    <t>Alim + décharge ok - en attente de la pose par AQUALEX</t>
+  </si>
+  <si>
+    <t>Jean-Louis - AQUALEX</t>
+  </si>
+  <si>
+    <t>Jean-Louis - Frank</t>
+  </si>
+  <si>
+    <t>BALTEAU - Matteino NIRO 0477/47.61.40</t>
+  </si>
+  <si>
+    <t>KONE - Mr Saint Viteux 0477/88.55.31</t>
+  </si>
+  <si>
+    <t>BEGELEC - Bart 02/569.65.27</t>
+  </si>
+  <si>
+    <t>EMOLIQUIDS - Nico JOLY 0475/290.302</t>
+  </si>
+  <si>
+    <t>SCREEN SERVICES - Valentin 0495/99.15.19</t>
+  </si>
+  <si>
+    <t>AEJ rénovations Varella 0492/59.90.72</t>
+  </si>
+  <si>
+    <t>ULTRASONS - Laurent 0472/72.00.22</t>
+  </si>
+  <si>
+    <t>LINERGY - Grégory SADZOT 0471/08.88.36</t>
+  </si>
+  <si>
+    <t>SKIDATA - helpdesk.bnlx@skidata.com</t>
+  </si>
+  <si>
+    <t>FLORATOIT - Mme BOURMANNE 0471/23.45.80</t>
+  </si>
+  <si>
+    <t>REXEL</t>
+  </si>
+  <si>
+    <t>ALL ACCES 02/387.43.32</t>
+  </si>
+  <si>
+    <t>listing chambre par chambre créé pour le suivi à relancer avec nouveau technicien</t>
+  </si>
+  <si>
+    <t>ODF</t>
+  </si>
+  <si>
+    <t>ICT + Jean-Louis</t>
+  </si>
+  <si>
+    <t>nouveau test du 10/08 au 17/08 - attente résultat sem 37</t>
+  </si>
+  <si>
+    <t>offre pour temporisation 2300€</t>
+  </si>
+  <si>
+    <t>reste radiateur</t>
+  </si>
+  <si>
+    <t>Etilux - Kevin 0498/16.55.84</t>
+  </si>
+  <si>
+    <t>Wallon 0478/32.62.39</t>
+  </si>
+  <si>
+    <t>PO a approuver</t>
+  </si>
+  <si>
+    <t>Romelio</t>
+  </si>
+  <si>
+    <t>Déjà demandé plusieurs fois à VIP WELLNESS - revient le 25/08 va finaliser suivant dernier appel</t>
+  </si>
+  <si>
+    <t>VIP WELLNESS ne finalise pas - revient le 25/08 va finaliser suivant dernier appel</t>
+  </si>
+  <si>
+    <t>service achats Liège - le couvreur n'a reçu aucune demande de Liège au 21/08/26</t>
+  </si>
+  <si>
+    <t>JMR</t>
+  </si>
+  <si>
+    <t>prise triphasée entrée hôtel (yacht et blue aussi possible ?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procédure </t>
+  </si>
+  <si>
+    <t>Commande ok attente planning</t>
+  </si>
+  <si>
+    <t>optimiser odeurs casino - dosage augmenté - test avec extracteur garage en cours</t>
+  </si>
+  <si>
+    <t>Nettoyage + démolitions +/- 15/08 - début travaux septembre - Attend le paiement de son acompte - PO signé le 03/09</t>
+  </si>
+  <si>
+    <t>Devis demandé chez ULTRASONS - rappel le 10/06
+prestataire à relancer - prototype semaine 33 - rappel le 18/08 et 21/08 - proto à modifier seront fait pour le 18/09</t>
+  </si>
+  <si>
+    <t>Visite pour second devis le 25/08 - attente devis min 2 semaines</t>
+  </si>
+  <si>
+    <t>1 des 2 à été remplacé, l'autre à un problème de communication - fournisseur cherche une solution - rappel fait le 04/08 - vient le 26/08 - repporté au 09/09 car fourniture pas reçue</t>
+  </si>
+  <si>
+    <t>commandé chez SKIDATA mais responsable ne travaille plus là… - rappel le 29/07 - rappel le 21/08 - pièce reçue mais pas possible de la changer nous-mêmes à cause des connecteurs électroniques</t>
+  </si>
+  <si>
+    <t>Rappel le 21/08 - transféré à qqn d'autre car le commercial ne travaille plus chez eux</t>
+  </si>
+  <si>
+    <t>Offre à recevoir rappel fait le 29/05
+demande envoyée à un autre prestataire - Assa Abloy ne fait plus ces portes - Demande faite chez un 3ème - Venu sur place le 21/08 pour devis - PO en approbation</t>
+  </si>
+  <si>
+    <t>RAL envoyé - prévu mi-aout - rappel le 21/08 - rappel le 04/09</t>
+  </si>
+  <si>
+    <t>Test ok mais signal trop faible nouvelle antenne wifi à installer dans quai de livraison - câble data à tirer</t>
+  </si>
+  <si>
+    <t>Rappel fait chez EQUANS 21/08 - ferronier sur place le 04/09 attente devis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vu avec BALTEAU le 14/08 - pas de possibilité avant début septembre (yacht et blue aussi possible ?) - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrien doit faire vider armoire local coffre pour déplacer armoires métalliques </t>
+  </si>
+  <si>
+    <t>2 demandes de prix demandées - rappel le 21/08 - Premier prix reçu 5900€ - second relancé</t>
+  </si>
+  <si>
+    <t>équipement de nouveau reparti pour analyse chez le fournisseur
+réparé mais à nouveau grillé - rappel le 04/09</t>
+  </si>
+  <si>
+    <t>prestataire passé, ça vient d'en bas - test avec ventilation prévu - dosage augmenté partout dans casino - test extracteur en cours</t>
+  </si>
+  <si>
+    <t>RENO ENERGIE variante en sous-sol commandée; ils font les démarches pour les pompiers; PO à approuver - reunion légal ENGIE pour contrat le 26/08 - PO ok paiement acompte semaine 37</t>
+  </si>
+  <si>
+    <t>Sterfput à créer et carrelage à acheter - date carrotage à recevoir du sous-traitant - visite semaine 37</t>
+  </si>
+  <si>
+    <t>Débuter ce 04/09</t>
+  </si>
+  <si>
+    <t>Jérôme Farinaux - contact société - la société qui était venue voir n'a jamais envoyé de devis, Jérôme ne retrouve rien - Nouvelles photos des façades envoyées à Jérome le 18/08 - visite ST le 02/09</t>
+  </si>
+  <si>
+    <t>Réparation provisoire réalisée car produit reçu n'était pas le bon - semaine 37</t>
+  </si>
+  <si>
+    <t>Marchandise chez nous mais en attente parce que si on change les bains à bulles on ne va pas monter les parois
+devis : 50k pour 11 - reprise des anciennes baignoires ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visite le 11/05 - devis en attente - dernier rappel le 22/05 - rappel par email + téléphone 05/06 - réception trespa pour réparation semaine 33 - porte prix à faire diminuer - plannifié semaine 35 - rappel le 21/08 : enverra le prix encore aujourd'hui - commande ok plannifié à la semaine 39
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouvel offre avec autre solution à recevoir - rappel le 21/08
+solution avec application à distance
+devis : 30k + système
+deuxième devis de Ultrason ? </t>
+  </si>
+  <si>
+    <t>Reste 8 chambres à faire en interne car difficile avec taux d'occupation</t>
+  </si>
+  <si>
+    <t>Stockage</t>
+  </si>
+  <si>
+    <t>compartimenter le local GP1</t>
+  </si>
+  <si>
+    <t>Nettoyage de printemps</t>
+  </si>
+  <si>
+    <t>Procédure groupe hydrophore</t>
+  </si>
+  <si>
+    <t>pour redémarrer la pompe</t>
+  </si>
+  <si>
+    <t>Bornes enlevées le 18/08 - JM ne veut plus les vitres
+Adrien : intéressé par les vitres ?</t>
+  </si>
+  <si>
+    <t>Eline</t>
+  </si>
+  <si>
+    <t>Derniers boitiers comme les nôtres reçu le 20/08 
+7 en stock</t>
+  </si>
+  <si>
+    <t>Jardisart fin septembre</t>
+  </si>
+  <si>
+    <t>listing chambre par chambre créé pour le suivi à relancer avec nouveau technicien (Quid)</t>
+  </si>
+  <si>
+    <t>Procédure écrite avec photo à réaliser pour HK, Réception</t>
+  </si>
+  <si>
+    <t>David doit bloquer des chambres pour pouvoir travailler = planning à voir (blocage hebdo défini, ex 3 tous les mardi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">à mettre dans les capex
+four, électricité, hotte et nouveau frigo traiteur… 
+devis à valider / besoin à définir </t>
   </si>
 </sst>
 </file>
@@ -889,7 +946,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -898,7 +955,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -947,9 +1016,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -959,11 +1025,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1033,10 +1114,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M100" totalsRowShown="0" dataDxfId="13">
-  <autoFilter ref="A1:M100" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M100">
-    <sortCondition ref="C1:C100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M99" totalsRowShown="0" dataDxfId="13">
+  <autoFilter ref="A1:M99" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M99">
+    <sortCondition ref="C1:C99"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4F006A25-C195-4CE0-BFA1-A12D1BA0DCFF}" name="Catégorie" dataDxfId="12"/>
@@ -1379,8 +1460,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M100"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M99"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.875" bestFit="1" customWidth="1"/>
@@ -1404,10 +1485,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1435,30 +1516,30 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="A2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="14">
         <v>46185</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1466,60 +1547,60 @@
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="A3" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="14">
         <v>46188</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="C4" s="14">
         <v>46188</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="7"/>
@@ -1540,27 +1621,27 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="A5" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="14">
         <v>46188</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1569,27 +1650,27 @@
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="A6" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="14">
         <v>46199</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1598,30 +1679,30 @@
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="A7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="14">
         <v>46199</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1629,30 +1710,30 @@
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="14">
         <v>46199</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1660,21 +1741,21 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="A9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="14">
         <v>46199</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="7"/>
@@ -1685,23 +1766,23 @@
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="A10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="14">
         <v>46199</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="7"/>
@@ -1712,27 +1793,27 @@
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="14">
         <v>46199</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>16</v>
@@ -1751,21 +1832,21 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="14">
         <v>46199</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="15"/>
+      <c r="G12" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="7" t="s">
@@ -1788,21 +1869,21 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="14">
         <v>46199</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="7" t="s">
@@ -1825,66 +1906,66 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="A14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="14">
         <v>46199</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="A15" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="14">
         <v>46199</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="12"/>
+      <c r="E15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>16</v>
@@ -1903,23 +1984,23 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="A16" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="14">
         <v>46199</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="12"/>
+      <c r="E16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="7" t="s">
@@ -1942,27 +2023,27 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="14">
         <v>46199</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="D17" s="12"/>
+      <c r="E17" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -1971,27 +2052,27 @@
       <c r="M17" s="3"/>
     </row>
     <row r="18" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="14">
         <v>46199</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>16</v>
@@ -2010,23 +2091,23 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="14">
         <v>46199</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="D19" s="12"/>
+      <c r="E19" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="7"/>
@@ -2037,23 +2118,23 @@
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="A20" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="14">
         <v>46199</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="D20" s="12"/>
+      <c r="E20" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="7"/>
@@ -2064,27 +2145,27 @@
       <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="4">
+      <c r="A21" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="14">
         <v>46201</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="D21" s="16"/>
+      <c r="E21" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -2093,30 +2174,30 @@
       <c r="M21" s="3"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="4">
+      <c r="A22" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="14">
         <v>46218</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="D22" s="12"/>
+      <c r="E22" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -2124,27 +2205,27 @@
       <c r="M22" s="3"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="B23" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="14">
         <v>46218</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="D23" s="12"/>
+      <c r="E23" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -2153,30 +2234,30 @@
       <c r="M23" s="3"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="14">
+        <v>46218</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="4">
-        <v>46218</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="I24" s="7" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>16</v>
@@ -2192,27 +2273,27 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="A25" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="14">
         <v>46233</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="6" t="s">
+      <c r="D25" s="12"/>
+      <c r="E25" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -2221,180 +2302,186 @@
       <c r="M25" s="3"/>
     </row>
     <row r="26" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="4">
-        <v>46244</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>40</v>
+      <c r="A26" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="14">
+        <v>46249</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I26" s="3"/>
+        <v>251</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="4">
-        <v>46248</v>
-      </c>
-      <c r="D27" s="5">
-        <v>46357</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>133</v>
+    <row r="27" spans="1:13" ht="63" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="14">
+        <v>46249</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C28" s="4">
+    <row r="28" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="14">
         <v>46249</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>49</v>
+      <c r="D28" s="12"/>
+      <c r="E28" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" ht="63" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="B29" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="14">
+        <v>46264</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>158</v>
+      <c r="G29" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>201</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
     <row r="30" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46387</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>28</v>
+      <c r="A30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="14">
+        <v>46264</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>206</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>40</v>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="14">
+        <v>46266</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>230</v>
+        <v>163</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -2404,26 +2491,26 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C32" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D32" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D32" s="5"/>
       <c r="E32" s="6" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2431,116 +2518,122 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C33" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D33" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D33" s="5"/>
       <c r="E33" s="6" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>118</v>
+        <v>44</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="C34" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D34" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46357</v>
+      </c>
       <c r="E34" s="6" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="I34" s="3"/>
+        <v>217</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C35" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D35" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D35" s="5">
+        <v>46387</v>
+      </c>
       <c r="E35" s="6" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="C36" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>254</v>
@@ -2551,31 +2644,31 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>107</v>
+        <v>23</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>97</v>
       </c>
       <c r="C37" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>255</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>157</v>
+        <v>229</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -2584,94 +2677,86 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>90</v>
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="C38" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D38" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D38" s="3"/>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>31</v>
+        <v>117</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="C39" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>94</v>
+        <v>121</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="C40" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>154</v>
+        <v>272</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -2679,44 +2764,46 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="4">
+        <v>46280</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="H41" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I41" s="3"/>
+        <v>274</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>12</v>
+        <v>121</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="C42" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="6" t="s">
@@ -2726,19 +2813,17 @@
         <v>14</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K42" s="7" t="s">
-        <v>257</v>
+      <c r="K42" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>16</v>
@@ -2747,28 +2832,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>106</v>
+        <v>121</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="C43" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="6" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>239</v>
+        <v>27</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>287</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -2776,64 +2861,62 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>87</v>
+        <v>121</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="C44" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D44" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="C45" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -2842,138 +2925,154 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>212</v>
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C46" s="4">
-        <v>46249</v>
-      </c>
-      <c r="D46" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D46" s="5"/>
       <c r="E46" s="6" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
+        <v>219</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>85</v>
+        <v>44</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="C47" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I47" s="3"/>
+        <v>259</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>262</v>
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="C48" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>270</v>
+        <v>121</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C49" s="4">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="6"/>
+      <c r="E49" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="F49" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H49" s="7"/>
+      <c r="H49" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>48</v>
+        <v>211</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="C50" s="4">
-        <v>46251</v>
-      </c>
-      <c r="D50" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D50" s="3"/>
       <c r="E50" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="I50" s="3"/>
+        <v>261</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -2981,55 +3080,53 @@
     </row>
     <row r="51" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="C51" s="4">
-        <v>46264</v>
+        <v>46280</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="E51" s="6"/>
       <c r="F51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I51" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="C52" s="4">
-        <v>46264</v>
+        <v>46280</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="E52" s="6"/>
       <c r="F52" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
@@ -3039,26 +3136,26 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>130</v>
+        <v>44</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="C53" s="4">
-        <v>46264</v>
+        <v>46280</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="6" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
@@ -3068,28 +3165,30 @@
     </row>
     <row r="54" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>73</v>
+        <v>23</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="C54" s="4">
-        <v>46264</v>
-      </c>
-      <c r="D54" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D54" s="3"/>
       <c r="E54" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="I54" s="3"/>
+        <v>265</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
@@ -3097,24 +3196,22 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>226</v>
+        <v>48</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="C55" s="4">
-        <v>46264</v>
+        <v>46280</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="G55" s="6"/>
       <c r="H55" s="7" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
@@ -3122,28 +3219,28 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>110</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="C56" s="4">
-        <v>46265</v>
-      </c>
-      <c r="D56" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D56" s="5"/>
       <c r="E56" s="6" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
@@ -3151,60 +3248,70 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="C57" s="4">
-        <v>46265</v>
-      </c>
-      <c r="D57" s="3"/>
+        <v>46280</v>
+      </c>
+      <c r="D57" s="5"/>
       <c r="E57" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="63" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="4">
+        <v>46280</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C58" s="4">
-        <v>46265</v>
-      </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="F58" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="H58" s="7" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -3213,22 +3320,26 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>249</v>
+        <v>117</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="C59" s="4">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="6"/>
+      <c r="E59" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="F59" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G59" s="6"/>
+      <c r="G59" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="H59" s="7" t="s">
-        <v>250</v>
+        <v>187</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
@@ -3236,28 +3347,28 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>114</v>
+        <v>44</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>209</v>
       </c>
       <c r="C60" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="6" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -3265,67 +3376,57 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C61" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D61" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="I61" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>68</v>
+      <c r="B62" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C62" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D62" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D62" s="3"/>
       <c r="E62" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>243</v>
+        <v>137</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
@@ -3333,32 +3434,30 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" ht="63" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>63</v>
+        <v>44</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C63" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D63" s="3"/>
-      <c r="E63" s="8" t="s">
-        <v>13</v>
+      <c r="E63" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>208</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
@@ -3366,26 +3465,26 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>70</v>
+        <v>44</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C64" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="6" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
@@ -3393,125 +3492,127 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>27</v>
+        <v>121</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="C65" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H65" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
     </row>
     <row r="66" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>261</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D66" s="5"/>
+        <v>46280</v>
+      </c>
+      <c r="D66" s="3"/>
       <c r="E66" s="6" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="H66" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>77</v>
+        <v>118</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="C67" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I67" s="3"/>
+        <v>152</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>75</v>
+        <v>43</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C68" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>146</v>
+        <v>270</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
@@ -3519,28 +3620,28 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>76</v>
+        <v>120</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="C69" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>146</v>
+        <v>271</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
@@ -3548,28 +3649,28 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>74</v>
+        <v>51</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>98</v>
       </c>
       <c r="C70" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
@@ -3579,26 +3680,26 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>115</v>
+        <v>51</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C71" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -3606,28 +3707,28 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>116</v>
+        <v>51</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C72" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
@@ -3637,52 +3738,42 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C73" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>117</v>
+        <v>51</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C74" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="6" t="s">
@@ -3692,14 +3783,12 @@
         <v>25</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
@@ -3707,67 +3796,53 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>188</v>
+        <v>249</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="C75" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46388</v>
-      </c>
+        <v>46280</v>
+      </c>
+      <c r="D75" s="3"/>
       <c r="E75" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="C76" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="6" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>172</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G76" s="6"/>
       <c r="H76" s="7" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -3775,28 +3850,28 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="C77" s="4">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="6" t="s">
-        <v>13</v>
+        <v>282</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>174</v>
+        <v>288</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
@@ -3804,30 +3879,32 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="C78" s="4">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I78" s="3"/>
+        <v>266</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -3835,26 +3912,26 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>82</v>
+        <v>44</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="C79" s="4">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="6" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
@@ -3864,55 +3941,63 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C80" s="4">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="6" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
-      <c r="M80" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="C81" s="4">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="D81" s="3"/>
-      <c r="E81" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="E81" s="6"/>
       <c r="F81" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
@@ -3922,13 +4007,13 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>83</v>
+        <v>120</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="C82" s="4">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="6" t="s">
@@ -3938,93 +4023,103 @@
         <v>25</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>250</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="C83" s="4">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="6" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>253</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>247</v>
+        <v>121</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="C84" s="4">
-        <v>46269</v>
+        <v>46296</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="6" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="H84" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="I84" s="3"/>
+        <v>273</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>267</v>
+        <v>122</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C85" s="4">
-        <v>46280</v>
+        <v>46310</v>
       </c>
       <c r="D85" s="3"/>
-      <c r="E85" s="6"/>
+      <c r="E85" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="F85" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
@@ -4034,104 +4129,84 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>50</v>
+        <v>122</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="C86" s="4">
-        <v>46295</v>
+        <v>46310</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="6" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>55</v>
+        <v>122</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="C87" s="4">
-        <v>46296</v>
+        <v>46310</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>86</v>
+        <v>44</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="C88" s="4">
-        <v>46310</v>
+        <v>46325</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="6" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>218</v>
+        <v>45</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
@@ -4141,26 +4216,26 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>66</v>
+        <v>44</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="C89" s="4">
-        <v>46310</v>
+        <v>46325</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="6" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>218</v>
+        <v>45</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
@@ -4170,140 +4245,124 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>108</v>
+        <v>118</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="C90" s="4">
-        <v>46310</v>
-      </c>
-      <c r="D90" s="3"/>
+        <v>46325</v>
+      </c>
+      <c r="D90" s="4">
+        <v>46388</v>
+      </c>
       <c r="E90" s="6" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
+        <v>192</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>181</v>
+        <v>276</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="C91" s="4">
-        <v>46388</v>
+        <v>46325</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>54</v>
+        <v>276</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="C92" s="4">
+        <v>46325</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C93" s="4">
         <v>46388</v>
       </c>
-      <c r="D92" s="3"/>
-      <c r="E92" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F92" s="6" t="s">
+      <c r="D93" s="3"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C93" s="4">
-        <v>46478</v>
-      </c>
-      <c r="D93" s="3"/>
-      <c r="E93" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="G93" s="6" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="7" t="s">
-        <v>202</v>
+      <c r="K93" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>16</v>
@@ -4314,84 +4373,104 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B94" s="12" t="s">
-        <v>62</v>
+        <v>48</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="C94" s="4">
-        <v>46508</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>46388</v>
+      </c>
+      <c r="D94" s="3"/>
       <c r="E94" s="6" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H94" s="7"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C95" s="4"/>
-      <c r="D95" s="5">
-        <v>46357</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" s="4">
+        <v>46478</v>
+      </c>
+      <c r="D95" s="3"/>
       <c r="E95" s="6" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
+        <v>213</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>64</v>
+        <v>44</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="5">
-        <v>46387</v>
+        <v>46357</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
@@ -4401,143 +4480,102 @@
     </row>
     <row r="97" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B97" s="13" t="s">
-        <v>189</v>
+        <v>44</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C97" s="4"/>
-      <c r="D97" s="3"/>
+      <c r="D97" s="5">
+        <v>46387</v>
+      </c>
       <c r="E97" s="6" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="3"/>
-      <c r="E98" s="6"/>
+      <c r="E98" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="F98" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="I98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J98" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K98" s="3" t="s">
+      <c r="L98" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L98" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M98" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="3"/>
-      <c r="E99" s="6" t="s">
-        <v>217</v>
-      </c>
+      <c r="E99" s="6"/>
       <c r="F99" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H99" s="7"/>
+        <v>167</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="I99" s="3" t="s">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H100" s="7"/>
-      <c r="I100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/suivi_taches.xlsx
+++ b/suivi_taches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D26EAE-6FA1-4F23-9276-72128FCB1E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65E0233-3772-4F21-ACE0-12D8AB092FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="293">
   <si>
     <t>Catégorie</t>
   </si>
@@ -443,9 +443,6 @@
     <t>DORMA</t>
   </si>
   <si>
-    <t>CHENE</t>
-  </si>
-  <si>
     <t>A programmer après peinture des chambres</t>
   </si>
   <si>
@@ -489,9 +486,6 @@
   </si>
   <si>
     <t>Concerné</t>
-  </si>
-  <si>
-    <t>Promate démonté</t>
   </si>
   <si>
     <t>Jean-Marc</t>
@@ -594,9 +588,6 @@
     <t>Ventilation canalisations casino pour odeurs</t>
   </si>
   <si>
-    <t>Engie, RenoEnergie, Interparking ?</t>
-  </si>
-  <si>
     <t>en même temps avec RenoEnergie</t>
   </si>
   <si>
@@ -646,9 +637,6 @@
   </si>
   <si>
     <t>procédure électricité</t>
-  </si>
-  <si>
-    <t>en attente de Jean-Louis</t>
   </si>
   <si>
     <t>Betting</t>
@@ -691,9 +679,6 @@
     <t>Hôtel</t>
   </si>
   <si>
-    <t>Plans reçu de BALTEAU envoyé chez BEGELEC et rappel fait le 14/08</t>
-  </si>
-  <si>
     <t>conteneur le 12/08
 à voir si quelqu'un peut venir les chercher - fait un conteneur 15 m3 évacué</t>
   </si>
@@ -743,33 +728,21 @@
     <t>ALL ACCES 02/387.43.32</t>
   </si>
   <si>
-    <t>listing chambre par chambre créé pour le suivi à relancer avec nouveau technicien</t>
-  </si>
-  <si>
     <t>ODF</t>
   </si>
   <si>
     <t>ICT + Jean-Louis</t>
   </si>
   <si>
-    <t>nouveau test du 10/08 au 17/08 - attente résultat sem 37</t>
-  </si>
-  <si>
     <t>offre pour temporisation 2300€</t>
   </si>
   <si>
-    <t>reste radiateur</t>
-  </si>
-  <si>
     <t>Etilux - Kevin 0498/16.55.84</t>
   </si>
   <si>
     <t>Wallon 0478/32.62.39</t>
   </si>
   <si>
-    <t>PO a approuver</t>
-  </si>
-  <si>
     <t>Romelio</t>
   </si>
   <si>
@@ -797,16 +770,6 @@
     <t>optimiser odeurs casino - dosage augmenté - test avec extracteur garage en cours</t>
   </si>
   <si>
-    <t>Nettoyage + démolitions +/- 15/08 - début travaux septembre - Attend le paiement de son acompte - PO signé le 03/09</t>
-  </si>
-  <si>
-    <t>Devis demandé chez ULTRASONS - rappel le 10/06
-prestataire à relancer - prototype semaine 33 - rappel le 18/08 et 21/08 - proto à modifier seront fait pour le 18/09</t>
-  </si>
-  <si>
-    <t>Visite pour second devis le 25/08 - attente devis min 2 semaines</t>
-  </si>
-  <si>
     <t>1 des 2 à été remplacé, l'autre à un problème de communication - fournisseur cherche une solution - rappel fait le 04/08 - vient le 26/08 - repporté au 09/09 car fourniture pas reçue</t>
   </si>
   <si>
@@ -814,22 +777,6 @@
   </si>
   <si>
     <t>Rappel le 21/08 - transféré à qqn d'autre car le commercial ne travaille plus chez eux</t>
-  </si>
-  <si>
-    <t>Offre à recevoir rappel fait le 29/05
-demande envoyée à un autre prestataire - Assa Abloy ne fait plus ces portes - Demande faite chez un 3ème - Venu sur place le 21/08 pour devis - PO en approbation</t>
-  </si>
-  <si>
-    <t>RAL envoyé - prévu mi-aout - rappel le 21/08 - rappel le 04/09</t>
-  </si>
-  <si>
-    <t>Test ok mais signal trop faible nouvelle antenne wifi à installer dans quai de livraison - câble data à tirer</t>
-  </si>
-  <si>
-    <t>Rappel fait chez EQUANS 21/08 - ferronier sur place le 04/09 attente devis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vu avec BALTEAU le 14/08 - pas de possibilité avant début septembre (yacht et blue aussi possible ?) - </t>
   </si>
   <si>
     <t xml:space="preserve">Adrien doit faire vider armoire local coffre pour déplacer armoires métalliques </t>
@@ -842,30 +789,13 @@
 réparé mais à nouveau grillé - rappel le 04/09</t>
   </si>
   <si>
-    <t>prestataire passé, ça vient d'en bas - test avec ventilation prévu - dosage augmenté partout dans casino - test extracteur en cours</t>
-  </si>
-  <si>
     <t>RENO ENERGIE variante en sous-sol commandée; ils font les démarches pour les pompiers; PO à approuver - reunion légal ENGIE pour contrat le 26/08 - PO ok paiement acompte semaine 37</t>
   </si>
   <si>
-    <t>Sterfput à créer et carrelage à acheter - date carrotage à recevoir du sous-traitant - visite semaine 37</t>
-  </si>
-  <si>
     <t>Débuter ce 04/09</t>
   </si>
   <si>
     <t>Jérôme Farinaux - contact société - la société qui était venue voir n'a jamais envoyé de devis, Jérôme ne retrouve rien - Nouvelles photos des façades envoyées à Jérome le 18/08 - visite ST le 02/09</t>
-  </si>
-  <si>
-    <t>Réparation provisoire réalisée car produit reçu n'était pas le bon - semaine 37</t>
-  </si>
-  <si>
-    <t>Marchandise chez nous mais en attente parce que si on change les bains à bulles on ne va pas monter les parois
-devis : 50k pour 11 - reprise des anciennes baignoires ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visite le 11/05 - devis en attente - dernier rappel le 22/05 - rappel par email + téléphone 05/06 - réception trespa pour réparation semaine 33 - porte prix à faire diminuer - plannifié semaine 35 - rappel le 21/08 : enverra le prix encore aujourd'hui - commande ok plannifié à la semaine 39
-</t>
   </si>
   <si>
     <t xml:space="preserve">Nouvel offre avec autre solution à recevoir - rappel le 21/08
@@ -874,9 +804,6 @@
 deuxième devis de Ultrason ? </t>
   </si>
   <si>
-    <t>Reste 8 chambres à faire en interne car difficile avec taux d'occupation</t>
-  </si>
-  <si>
     <t>Stockage</t>
   </si>
   <si>
@@ -890,10 +817,6 @@
   </si>
   <si>
     <t>pour redémarrer la pompe</t>
-  </si>
-  <si>
-    <t>Bornes enlevées le 18/08 - JM ne veut plus les vitres
-Adrien : intéressé par les vitres ?</t>
   </si>
   <si>
     <t>Eline</t>
@@ -906,18 +829,106 @@
     <t>Jardisart fin septembre</t>
   </si>
   <si>
-    <t>listing chambre par chambre créé pour le suivi à relancer avec nouveau technicien (Quid)</t>
-  </si>
-  <si>
     <t>Procédure écrite avec photo à réaliser pour HK, Réception</t>
   </si>
   <si>
     <t>David doit bloquer des chambres pour pouvoir travailler = planning à voir (blocage hebdo défini, ex 3 tous les mardi)</t>
   </si>
   <si>
-    <t xml:space="preserve">à mettre dans les capex
+    <t>nouveau test du 10/08 au 17/08 - attente résultat sem 37 - rappel fait le 18/09</t>
+  </si>
+  <si>
+    <t>Reste 4 chambres à faire en interne car difficile avec taux d'occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans reçu de BALTEAU envoyé chez BEGELEC et rappel fait le 14/08 - PO ok et commande envoyée le  </t>
+  </si>
+  <si>
+    <t>Démolition commencée</t>
+  </si>
+  <si>
+    <t>Devis 1 : 13.000 Devis 2 : 19.700 Devis 3 : en attente</t>
+  </si>
+  <si>
+    <t>Marchandise chez nous mais en attente parce que si on change les bains à bulles on ne va pas monter les parois
+devis : 50k pour 11 - reprise des anciennes baignoires oui mais uniquement pour nous en débarrasser voir offre mise à jour</t>
+  </si>
+  <si>
+    <t>PO OK - cde OK - attente paiement acompte</t>
+  </si>
+  <si>
+    <t>Test ok mais signal trop faible nouvelle antenne wifi à installer dans quai de livraison - câble data à tirer - reçu antenne wifi ICT cette semaine</t>
+  </si>
+  <si>
+    <t>tableau envoyé à Dyler pour bloquer des chambres  pour joints,…</t>
+  </si>
+  <si>
+    <t>Rappel fait chez EQUANS 21/08 - ferronier sur place le 04/09 attente devis - devis 1 5900€ - deuxième demandé</t>
+  </si>
+  <si>
+    <t>Vu avec BALTEAU le 14/08 - pas de possibilité avant début septembre (yacht et blue aussi possible ?) - semaine 39</t>
+  </si>
+  <si>
+    <t>reste radiateur à refixer</t>
+  </si>
+  <si>
+    <t>en attente de Jean-Louis - pas eu le temps cette semaine</t>
+  </si>
+  <si>
+    <t>PO a approuver - à modifier veulent venir voir les accès</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sterfput à créer et carrelage à acheter - date carrotage à recevoir du sous-traitant - visite semaine 37 </t>
+  </si>
+  <si>
+    <t>Promate démonté - prévu 30/09</t>
+  </si>
+  <si>
+    <t>Réparation provisoire réalisée car produit reçu n'était pas le bon - semaine 37 - 1 sur 3 fait car trop de passage et sol mouillé</t>
+  </si>
+  <si>
+    <t>Bornes enlevées le 18/08 - JM ne veut plus les vitres
+Adrien : intéressé par les vitres ? Portique démonté</t>
+  </si>
+  <si>
+    <t>à mettre dans les capex
 four, électricité, hotte et nouveau frigo traiteur… 
-devis à valider / besoin à définir </t>
+devis à valider / besoin à définir - offres de prix transférées à Eline</t>
+  </si>
+  <si>
+    <t>prestataire passé, ça vient d'en bas - test avec ventilation prévu - dosage augmenté partout dans casino - test extracteur en cours - sterfput sanitaires hommes casino remplacé</t>
+  </si>
+  <si>
+    <t>Devis demandé chez ULTRASONS - rappel le 10/06
+prestataire à relancer - prototype semaine 33 - rappel le 18/08 et 21/08 - proto à modifier seront fait pour le 18/09 - n'a pas tenu ses engagements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visite le 11/05 - devis en attente - dernier rappel le 22/05 - rappel par email + téléphone 05/06 - réception trespa pour réparation semaine 33 - porte prix à faire diminuer - plannifié semaine 35 - rappel le 21/08 : enverra le prix encore aujourd'hui - commande ok plannifié à la semaine 39 - prévu 22/09 mais on ne va pas remplacer des bacs si les plantes sont mortes
+</t>
+  </si>
+  <si>
+    <t>Passera voir le poteau lundi 21/09 et proposition de réunion le 23/09</t>
+  </si>
+  <si>
+    <t>CHENE - a.chene@chene.be</t>
+  </si>
+  <si>
+    <t>Engie (christophe.schiemsky@engie.com)/ RenoEnergie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Démontage des fumoirs </t>
+  </si>
+  <si>
+    <t>Arrêt intervention et entretien par Euromate - Prévoir démontage des fumoirs présents d’ici la fin de cette année</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euromate  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Séparation des terrasses </t>
+  </si>
+  <si>
+    <t>Dalle plancher "thé dansant"</t>
   </si>
 </sst>
 </file>
@@ -939,11 +950,12 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -967,7 +979,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -990,10 +1002,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1022,9 +1035,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1046,8 +1056,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
@@ -1114,8 +1132,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M99" totalsRowShown="0" dataDxfId="13">
-  <autoFilter ref="A1:M99" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M103" totalsRowShown="0" dataDxfId="13">
+  <autoFilter ref="A1:M103" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M99">
     <sortCondition ref="C1:C99"/>
   </sortState>
@@ -1460,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
@@ -1485,10 +1503,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1516,27 +1534,27 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>46185</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>134</v>
@@ -1547,23 +1565,23 @@
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>46188</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="7"/>
@@ -1584,23 +1602,23 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>46188</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="7"/>
@@ -1621,27 +1639,27 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>46188</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="15"/>
+      <c r="E5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1650,27 +1668,27 @@
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <v>46199</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="15" t="s">
+      <c r="D6" s="15"/>
+      <c r="E6" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1679,27 +1697,27 @@
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>46199</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>135</v>
@@ -1710,30 +1728,30 @@
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>46199</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="15" t="s">
+      <c r="D8" s="11"/>
+      <c r="E8" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="I8" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1741,21 +1759,21 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>46199</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="11"/>
+      <c r="E9" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="7"/>
@@ -1766,23 +1784,23 @@
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <v>46199</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="15" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="7"/>
@@ -1793,27 +1811,27 @@
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>46199</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="15" t="s">
+      <c r="F11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>16</v>
@@ -1832,21 +1850,21 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="13">
         <v>46199</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="15" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="14"/>
+      <c r="G12" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="7" t="s">
@@ -1869,21 +1887,21 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <v>46199</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="11"/>
+      <c r="E13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15" t="s">
+      <c r="F13" s="14"/>
+      <c r="G13" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="7" t="s">
@@ -1906,144 +1924,144 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="13">
+        <v>46199</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C14" s="14">
+      <c r="I14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="13">
         <v>46199</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="15" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="15" t="s">
+      <c r="F15" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="H15" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="14">
+      <c r="B16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="13">
         <v>46199</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="15" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="15" t="s">
+      <c r="F16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="H16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="13">
         <v>46199</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="15" t="s">
+      <c r="D17" s="11"/>
+      <c r="E17" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="14">
-        <v>46199</v>
-      </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>20</v>
-      </c>
       <c r="H17" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -2052,27 +2070,27 @@
       <c r="M17" s="3"/>
     </row>
     <row r="18" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13">
         <v>46199</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="15" t="s">
+      <c r="D18" s="11"/>
+      <c r="E18" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>16</v>
@@ -2091,23 +2109,23 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>46199</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="15" t="s">
+      <c r="D19" s="11"/>
+      <c r="E19" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="7"/>
@@ -2118,23 +2136,23 @@
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <v>46199</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="15" t="s">
+      <c r="D20" s="11"/>
+      <c r="E20" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="15" t="s">
+      <c r="F20" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="7"/>
@@ -2145,27 +2163,27 @@
       <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <v>46201</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="15" t="s">
+      <c r="D21" s="15"/>
+      <c r="E21" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -2174,27 +2192,27 @@
       <c r="M21" s="3"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>46218</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="15" t="s">
+      <c r="D22" s="11"/>
+      <c r="E22" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="15" t="s">
+      <c r="F22" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>129</v>
@@ -2205,27 +2223,27 @@
       <c r="M22" s="3"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <v>46218</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="15" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -2234,30 +2252,30 @@
       <c r="M23" s="3"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="13">
         <v>46218</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="15" t="s">
+      <c r="D24" s="11"/>
+      <c r="E24" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="15" t="s">
+      <c r="F24" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>16</v>
@@ -2273,27 +2291,27 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <v>46233</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="15" t="s">
+      <c r="D25" s="11"/>
+      <c r="E25" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="15" t="s">
+      <c r="F25" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -2302,28 +2320,28 @@
       <c r="M25" s="3"/>
     </row>
     <row r="26" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="A26" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="13">
         <v>46249</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="15" t="s">
+      <c r="D26" s="15"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2331,30 +2349,30 @@
       <c r="M26" s="3"/>
     </row>
     <row r="27" spans="1:13" ht="63" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <v>46249</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="15" t="s">
+      <c r="D27" s="11"/>
+      <c r="E27" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -2362,27 +2380,27 @@
       <c r="M27" s="3"/>
     </row>
     <row r="28" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13">
         <v>46249</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="15" t="s">
+      <c r="D28" s="11"/>
+      <c r="E28" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="15" t="s">
+      <c r="F28" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>16</v>
@@ -2391,7 +2409,7 @@
         <v>16</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>16</v>
@@ -2401,30 +2419,30 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13">
         <v>46264</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="F29" s="15" t="s">
+      <c r="D29" s="11"/>
+      <c r="E29" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2432,27 +2450,27 @@
       <c r="M29" s="3"/>
     </row>
     <row r="30" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13">
         <v>46264</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="15" t="s">
+      <c r="D30" s="15"/>
+      <c r="E30" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="15" t="s">
+      <c r="F30" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -2461,27 +2479,27 @@
       <c r="M30" s="3"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13">
         <v>46266</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="15" t="s">
+      <c r="D31" s="11"/>
+      <c r="E31" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="15" t="s">
+      <c r="F31" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="14" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -2489,7 +2507,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>44</v>
       </c>
@@ -2510,7 +2528,7 @@
         <v>27</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2539,10 +2557,10 @@
         <v>27</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2553,7 +2571,7 @@
       <c r="A34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C34" s="4">
@@ -2569,20 +2587,20 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
@@ -2605,17 +2623,17 @@
         <v>27</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>48</v>
       </c>
@@ -2636,7 +2654,7 @@
         <v>127</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -2662,13 +2680,13 @@
         <v>14</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -2687,7 +2705,7 @@
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>14</v>
@@ -2696,7 +2714,7 @@
         <v>39</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -2725,17 +2743,17 @@
         <v>27</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>121</v>
       </c>
@@ -2756,7 +2774,7 @@
         <v>127</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -2785,10 +2803,10 @@
         <v>127</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -2815,8 +2833,8 @@
       <c r="G42" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H42" s="17" t="s">
-        <v>286</v>
+      <c r="H42" s="16" t="s">
+        <v>261</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
@@ -2853,7 +2871,7 @@
         <v>27</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -2879,20 +2897,20 @@
         <v>14</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" ht="63" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -2913,10 +2931,10 @@
         <v>27</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -2944,10 +2962,10 @@
         <v>127</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>128</v>
@@ -2977,29 +2995,29 @@
         <v>127</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>136</v>
+        <v>286</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C48" s="4">
         <v>46280</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>14</v>
@@ -3008,10 +3026,10 @@
         <v>45</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
@@ -3039,7 +3057,7 @@
         <v>15</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -3049,10 +3067,10 @@
     </row>
     <row r="50" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C50" s="4">
         <v>46280</v>
@@ -3068,7 +3086,7 @@
         <v>45</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>129</v>
@@ -3080,10 +3098,10 @@
     </row>
     <row r="51" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C51" s="4">
         <v>46280</v>
@@ -3097,10 +3115,10 @@
         <v>15</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -3112,7 +3130,7 @@
         <v>116</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C52" s="4">
         <v>46280</v>
@@ -3126,7 +3144,7 @@
         <v>45</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
@@ -3155,7 +3173,7 @@
         <v>27</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
@@ -3184,10 +3202,10 @@
         <v>27</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
@@ -3199,7 +3217,7 @@
         <v>48</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C55" s="4">
         <v>46280</v>
@@ -3211,7 +3229,7 @@
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="7" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
@@ -3240,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
@@ -3269,16 +3287,16 @@
         <v>27</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>16</v>
@@ -3298,7 +3316,7 @@
         <v>46280</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="6" t="s">
@@ -3308,10 +3326,10 @@
         <v>27</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>186</v>
+        <v>287</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -3339,7 +3357,7 @@
         <v>27</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
@@ -3352,7 +3370,7 @@
         <v>44</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C60" s="4">
         <v>46280</v>
@@ -3368,7 +3386,7 @@
         <v>127</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -3397,7 +3415,7 @@
         <v>45</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
@@ -3426,7 +3444,7 @@
         <v>45</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
@@ -3455,7 +3473,7 @@
         <v>45</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
@@ -3481,10 +3499,10 @@
         <v>14</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
@@ -3512,8 +3530,8 @@
       <c r="G65" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H65" s="17" t="s">
-        <v>285</v>
+      <c r="H65" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
@@ -3541,8 +3559,8 @@
       <c r="G66" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H66" s="17" t="s">
-        <v>285</v>
+      <c r="H66" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>16</v>
@@ -3581,10 +3599,10 @@
         <v>27</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>152</v>
+        <v>278</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -3609,10 +3627,10 @@
         <v>14</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
@@ -3620,7 +3638,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>120</v>
       </c>
@@ -3641,7 +3659,7 @@
         <v>27</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
@@ -3670,7 +3688,7 @@
         <v>39</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
@@ -3699,7 +3717,7 @@
         <v>39</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -3728,7 +3746,7 @@
         <v>27</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
@@ -3757,7 +3775,7 @@
         <v>39</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
@@ -3786,7 +3804,7 @@
         <v>39</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
@@ -3796,10 +3814,10 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="C75" s="4">
         <v>46280</v>
@@ -3815,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
@@ -3825,10 +3843,10 @@
     </row>
     <row r="76" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C76" s="4">
         <v>46280</v>
@@ -3842,7 +3860,7 @@
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -3850,19 +3868,19 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C77" s="4">
         <v>46280</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="6" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>25</v>
@@ -3871,7 +3889,7 @@
         <v>45</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
@@ -3879,12 +3897,12 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C78" s="4">
         <v>46295</v>
@@ -3900,10 +3918,10 @@
         <v>27</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
@@ -3931,7 +3949,7 @@
         <v>45</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
@@ -3957,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>16</v>
@@ -3997,7 +4015,7 @@
         <v>45</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
@@ -4026,17 +4044,17 @@
         <v>39</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>117</v>
       </c>
@@ -4048,7 +4066,7 @@
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>14</v>
@@ -4057,17 +4075,17 @@
         <v>39</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="126" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>121</v>
       </c>
@@ -4088,10 +4106,10 @@
         <v>27</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
@@ -4116,10 +4134,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
@@ -4145,10 +4163,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
@@ -4174,10 +4192,10 @@
         <v>14</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
@@ -4197,7 +4215,7 @@
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -4206,7 +4224,7 @@
         <v>45</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
@@ -4226,7 +4244,7 @@
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>25</v>
@@ -4235,7 +4253,7 @@
         <v>45</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
@@ -4248,7 +4266,7 @@
         <v>118</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C90" s="4">
         <v>46325</v>
@@ -4263,10 +4281,10 @@
         <v>14</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>16</v>
@@ -4286,10 +4304,10 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C91" s="4">
         <v>46325</v>
@@ -4311,10 +4329,10 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="C92" s="4">
         <v>46325</v>
@@ -4339,7 +4357,7 @@
         <v>23</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C93" s="4">
         <v>46388</v>
@@ -4350,10 +4368,10 @@
         <v>25</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>40</v>
@@ -4362,7 +4380,7 @@
         <v>16</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>16</v>
@@ -4389,19 +4407,19 @@
         <v>25</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>16</v>
@@ -4422,16 +4440,16 @@
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>33</v>
@@ -4440,7 +4458,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>16</v>
@@ -4470,7 +4488,7 @@
         <v>127</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
@@ -4490,7 +4508,7 @@
         <v>46387</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>14</v>
@@ -4499,7 +4517,7 @@
         <v>45</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
@@ -4512,7 +4530,7 @@
         <v>118</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="3"/>
@@ -4523,10 +4541,10 @@
         <v>14</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>16</v>
@@ -4549,7 +4567,7 @@
         <v>23</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="3"/>
@@ -4558,13 +4576,13 @@
         <v>25</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>16</v>
@@ -4578,6 +4596,105 @@
       <c r="M99" s="3" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="100" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B100" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="C100" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C101" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="C102" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H102" s="7"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H106" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
